--- a/TesisFinal/ResultadoNUEVOS.xlsx
+++ b/TesisFinal/ResultadoNUEVOS.xlsx
@@ -8,16 +8,28 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://alumnosuaicl-my.sharepoint.com/personal/matia_fernandez_alumnos_uai_cl/Documents/Industrial/Magister/Codigos/TesisDefinitivo/TesisFinal/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="142" documentId="11_AD4D2F04E46CFB4ACB3E20986D90D3BC693EDF26" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{626ED0F6-8A75-4629-80D9-CCE1EBC17CD6}"/>
+  <xr:revisionPtr revIDLastSave="218" documentId="11_AD4D2F04E46CFB4ACB3E20986D90D3BC693EDF26" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F57BB964-F822-486F-B73B-FC70DB8736D7}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
+    <sheet name="480 25C" sheetId="3" r:id="rId2"/>
+    <sheet name="480" sheetId="2" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="_xlchart.v1.0" hidden="1">Hoja1!$B$1</definedName>
     <definedName name="_xlchart.v1.1" hidden="1">Hoja1!$B$2:$B$20</definedName>
+    <definedName name="_xlchart.v1.10" hidden="1">'480 25C'!$B$1</definedName>
+    <definedName name="_xlchart.v1.11" hidden="1">'480 25C'!$B$2:$B$20</definedName>
+    <definedName name="_xlchart.v1.12" hidden="1">'480 25C'!$C$1</definedName>
+    <definedName name="_xlchart.v1.13" hidden="1">'480 25C'!$C$2:$C$20</definedName>
+    <definedName name="_xlchart.v1.14" hidden="1">'480 25C'!$D$1</definedName>
+    <definedName name="_xlchart.v1.15" hidden="1">'480 25C'!$D$2:$D$20</definedName>
+    <definedName name="_xlchart.v1.16" hidden="1">'480 25C'!$E$1</definedName>
+    <definedName name="_xlchart.v1.17" hidden="1">'480 25C'!$E$2:$E$20</definedName>
+    <definedName name="_xlchart.v1.18" hidden="1">'480 25C'!$F$1</definedName>
+    <definedName name="_xlchart.v1.19" hidden="1">'480 25C'!$F$2:$F$20</definedName>
     <definedName name="_xlchart.v1.2" hidden="1">Hoja1!$C$1</definedName>
     <definedName name="_xlchart.v1.3" hidden="1">Hoja1!$C$2:$C$20</definedName>
     <definedName name="_xlchart.v1.4" hidden="1">Hoja1!$D$1</definedName>
@@ -27,17 +39,28 @@
     <definedName name="_xlchart.v1.8" hidden="1">Hoja1!$F$1</definedName>
     <definedName name="_xlchart.v1.9" hidden="1">Hoja1!$F$2:$F$20</definedName>
   </definedNames>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="6">
   <si>
     <t>Instancia</t>
   </si>
@@ -253,7 +276,160 @@
 </cx:chartSpace>
 </file>
 
+<file path=xl/charts/chartEx2.xml><?xml version="1.0" encoding="utf-8"?>
+<cx:chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex">
+  <cx:chartData>
+    <cx:data id="0">
+      <cx:numDim type="val">
+        <cx:f>_xlchart.v1.11</cx:f>
+      </cx:numDim>
+    </cx:data>
+    <cx:data id="1">
+      <cx:numDim type="val">
+        <cx:f>_xlchart.v1.13</cx:f>
+      </cx:numDim>
+    </cx:data>
+    <cx:data id="2">
+      <cx:numDim type="val">
+        <cx:f>_xlchart.v1.15</cx:f>
+      </cx:numDim>
+    </cx:data>
+    <cx:data id="3">
+      <cx:numDim type="val">
+        <cx:f>_xlchart.v1.17</cx:f>
+      </cx:numDim>
+    </cx:data>
+    <cx:data id="4">
+      <cx:numDim type="val">
+        <cx:f>_xlchart.v1.19</cx:f>
+      </cx:numDim>
+    </cx:data>
+  </cx:chartData>
+  <cx:chart>
+    <cx:title pos="t" align="ctr" overlay="0"/>
+    <cx:plotArea>
+      <cx:plotAreaRegion>
+        <cx:series layoutId="boxWhisker" uniqueId="{6A0E73EE-3977-400E-B114-A63C199AEE44}">
+          <cx:tx>
+            <cx:txData>
+              <cx:f>_xlchart.v1.10</cx:f>
+              <cx:v>S</cx:v>
+            </cx:txData>
+          </cx:tx>
+          <cx:dataId val="0"/>
+          <cx:layoutPr>
+            <cx:visibility meanLine="0" meanMarker="1" nonoutliers="0" outliers="1"/>
+            <cx:statistics quartileMethod="exclusive"/>
+          </cx:layoutPr>
+        </cx:series>
+        <cx:series layoutId="boxWhisker" uniqueId="{76E45336-7523-4A75-8B9F-DB01BEE372A8}">
+          <cx:tx>
+            <cx:txData>
+              <cx:f>_xlchart.v1.12</cx:f>
+              <cx:v>C</cx:v>
+            </cx:txData>
+          </cx:tx>
+          <cx:dataId val="1"/>
+          <cx:layoutPr>
+            <cx:visibility meanLine="0" meanMarker="1" nonoutliers="0" outliers="1"/>
+            <cx:statistics quartileMethod="exclusive"/>
+          </cx:layoutPr>
+        </cx:series>
+        <cx:series layoutId="boxWhisker" uniqueId="{75E5F308-BA13-4ED5-8FE3-DBBDE70C11C4}">
+          <cx:tx>
+            <cx:txData>
+              <cx:f>_xlchart.v1.14</cx:f>
+              <cx:v>RS</cx:v>
+            </cx:txData>
+          </cx:tx>
+          <cx:dataId val="2"/>
+          <cx:layoutPr>
+            <cx:visibility meanLine="0" meanMarker="1" nonoutliers="0" outliers="1"/>
+            <cx:statistics quartileMethod="exclusive"/>
+          </cx:layoutPr>
+        </cx:series>
+        <cx:series layoutId="boxWhisker" uniqueId="{A867E498-6283-4C12-9A61-23E339854324}">
+          <cx:tx>
+            <cx:txData>
+              <cx:f>_xlchart.v1.16</cx:f>
+              <cx:v>RC</cx:v>
+            </cx:txData>
+          </cx:tx>
+          <cx:dataId val="3"/>
+          <cx:layoutPr>
+            <cx:visibility meanLine="0" meanMarker="1" nonoutliers="0" outliers="1"/>
+            <cx:statistics quartileMethod="exclusive"/>
+          </cx:layoutPr>
+        </cx:series>
+        <cx:series layoutId="boxWhisker" uniqueId="{2E46BEFA-3A0F-4E24-BCC6-9649027505DB}">
+          <cx:tx>
+            <cx:txData>
+              <cx:f>_xlchart.v1.18</cx:f>
+              <cx:v>MC</cx:v>
+            </cx:txData>
+          </cx:tx>
+          <cx:dataId val="4"/>
+          <cx:layoutPr>
+            <cx:visibility meanLine="0" meanMarker="1" nonoutliers="0" outliers="1"/>
+            <cx:statistics quartileMethod="exclusive"/>
+          </cx:layoutPr>
+        </cx:series>
+      </cx:plotAreaRegion>
+      <cx:axis id="0">
+        <cx:catScaling gapWidth="1"/>
+        <cx:tickLabels/>
+      </cx:axis>
+      <cx:axis id="1">
+        <cx:valScaling min="400000"/>
+        <cx:majorGridlines/>
+        <cx:tickLabels/>
+      </cx:axis>
+    </cx:plotArea>
+  </cx:chart>
+</cx:chartSpace>
+</file>
+
 <file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors2.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
   <a:schemeClr val="accent1"/>
   <a:schemeClr val="accent2"/>
@@ -850,6 +1026,521 @@
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
       <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="406">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat">
+        <a:solidFill>
+          <a:srgbClr val="D9D9D9"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDash"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
     </cs:fontRef>
   </cs:wall>
 </cs:chartStyle>
@@ -938,6 +1629,177 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>16728</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>44450</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>449825</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>85171</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Imagen 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A327100C-B1E5-F5BE-C521-1C5157861FD0}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7636728" y="781050"/>
+          <a:ext cx="3481097" cy="1882221"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>600075</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>104775</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>600075</xdr:colOff>
+      <xdr:row>37</xdr:row>
+      <xdr:rowOff>85725</xdr:rowOff>
+    </xdr:to>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" Requires="cx1">
+        <xdr:graphicFrame macro="">
+          <xdr:nvGraphicFramePr>
+            <xdr:cNvPr id="4" name="Gráfico 3">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D5D82195-8127-F823-5668-81124F9DA5DA}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvGraphicFramePr/>
+          </xdr:nvGraphicFramePr>
+          <xdr:xfrm>
+            <a:off x="0" y="0"/>
+            <a:ext cx="0" cy="0"/>
+          </xdr:xfrm>
+          <a:graphic>
+            <a:graphicData uri="http://schemas.microsoft.com/office/drawing/2014/chartex">
+              <cx:chart xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+            </a:graphicData>
+          </a:graphic>
+        </xdr:graphicFrame>
+      </mc:Choice>
+      <mc:Fallback>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="0" name=""/>
+            <xdr:cNvSpPr>
+              <a:spLocks noTextEdit="1"/>
+            </xdr:cNvSpPr>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="600075" y="4156075"/>
+              <a:ext cx="4572000" cy="2743200"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:solidFill>
+              <a:prstClr val="white"/>
+            </a:solidFill>
+            <a:ln w="1">
+              <a:solidFill>
+                <a:prstClr val="green"/>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:r>
+                <a:rPr lang="es-CL" sz="1100"/>
+                <a:t>Este gráfico no está disponible en su versión de Excel.
+Si edita esta forma o guarda el libro en un formato de archivo diferente, el gráfico no se podrá utilizar.</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>749300</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>44537</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>392669</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>69292</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="Imagen 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1A5FD786-7878-DCFC-BFC3-BD966AEBA6F6}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7607300" y="3359237"/>
+          <a:ext cx="3453369" cy="1866255"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
 <file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
 <personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
@@ -952,6 +1814,36 @@
     <tableColumn id="4" xr3:uid="{D1A15D30-7641-4F97-BB39-CD9A7B5E2241}" name="RS"/>
     <tableColumn id="5" xr3:uid="{E18563C8-B1CD-4606-9B01-52D0A7590CBE}" name="RC"/>
     <tableColumn id="6" xr3:uid="{6AEC443D-ABCA-49C0-9688-1ECC6E819BE5}" name="MC"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{CF3EC788-574D-49FC-BD40-A7B914475A65}" name="Tabla134" displayName="Tabla134" ref="A1:F20" totalsRowShown="0">
+  <autoFilter ref="A1:F20" xr:uid="{CF3EC788-574D-49FC-BD40-A7B914475A65}"/>
+  <tableColumns count="6">
+    <tableColumn id="1" xr3:uid="{D5EA166B-7AE8-4BCF-AEA0-89AF8DE31E5F}" name="Instancia"/>
+    <tableColumn id="2" xr3:uid="{1121EE78-E114-496B-BE56-62E071E6C438}" name="S"/>
+    <tableColumn id="3" xr3:uid="{2379E95B-E115-43E7-A536-5C69D23B3D4F}" name="C"/>
+    <tableColumn id="4" xr3:uid="{3FF60F9F-22AF-4FA0-BC25-11D94B1CE10D}" name="RS"/>
+    <tableColumn id="5" xr3:uid="{73AF535C-6755-4DE7-A6A8-754F77D6B9FB}" name="RC"/>
+    <tableColumn id="6" xr3:uid="{D1C06327-2EB6-492A-8275-41C24A72E709}" name="MC"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{2BB2D810-1F00-4796-82FD-188565AF0659}" name="Tabla13" displayName="Tabla13" ref="A1:F20" totalsRowShown="0">
+  <autoFilter ref="A1:F20" xr:uid="{2BB2D810-1F00-4796-82FD-188565AF0659}"/>
+  <tableColumns count="6">
+    <tableColumn id="1" xr3:uid="{22FEF464-DFD2-46F5-8F94-5B11467ED66A}" name="Instancia"/>
+    <tableColumn id="2" xr3:uid="{42E0ECE8-4DFA-43DB-84D0-C4368B166EB6}" name="S"/>
+    <tableColumn id="3" xr3:uid="{9613B486-E85D-4D77-A061-D462C1599B94}" name="C"/>
+    <tableColumn id="4" xr3:uid="{30C93E5D-D36A-4CDA-8501-F98AFD041037}" name="RS"/>
+    <tableColumn id="5" xr3:uid="{2DB03AE2-24ED-4DE5-BF97-D968DB136348}" name="RC"/>
+    <tableColumn id="6" xr3:uid="{DD8D8AD8-B65D-4AD6-84A0-DDF02A0563FB}" name="MC"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1635,4 +2527,418 @@
     <tablePart r:id="rId2"/>
   </tableParts>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D538018C-AE31-499F-9187-4BAC09A67F15}">
+  <dimension ref="A1:K20"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetData>
+    <row r="1" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>650771</v>
+      </c>
+      <c r="C2">
+        <v>957431</v>
+      </c>
+      <c r="D2">
+        <v>792708</v>
+      </c>
+      <c r="E2">
+        <v>877620</v>
+      </c>
+      <c r="F2">
+        <v>472747</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <v>671985</v>
+      </c>
+      <c r="C3">
+        <v>811696</v>
+      </c>
+      <c r="D3">
+        <v>857758</v>
+      </c>
+      <c r="E3">
+        <v>914480</v>
+      </c>
+      <c r="F3">
+        <v>658358</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4">
+        <v>745290</v>
+      </c>
+      <c r="C4">
+        <v>876335</v>
+      </c>
+      <c r="D4">
+        <v>889793</v>
+      </c>
+      <c r="E4">
+        <v>904182</v>
+      </c>
+      <c r="F4">
+        <v>536897</v>
+      </c>
+      <c r="K4">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5">
+        <v>644723</v>
+      </c>
+      <c r="C5">
+        <v>1217738</v>
+      </c>
+      <c r="D5">
+        <v>945555</v>
+      </c>
+      <c r="E5">
+        <v>1050800</v>
+      </c>
+      <c r="F5">
+        <v>554045</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6">
+        <v>858204</v>
+      </c>
+      <c r="C6">
+        <v>842624</v>
+      </c>
+      <c r="D6">
+        <v>1004127</v>
+      </c>
+      <c r="E6">
+        <v>1061002</v>
+      </c>
+      <c r="F6">
+        <v>642569</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7">
+        <v>700780</v>
+      </c>
+      <c r="C7">
+        <v>946780</v>
+      </c>
+      <c r="D7">
+        <v>1067656</v>
+      </c>
+      <c r="E7">
+        <v>976770</v>
+      </c>
+      <c r="F7">
+        <v>526079</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8">
+        <v>719237</v>
+      </c>
+      <c r="C8">
+        <v>1084069</v>
+      </c>
+      <c r="D8">
+        <v>925692</v>
+      </c>
+      <c r="E8">
+        <v>888626</v>
+      </c>
+      <c r="F8">
+        <v>535247</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A9">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A10">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A11">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A12">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A13">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A14">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A15">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A16">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A17">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A18">
+        <v>17</v>
+      </c>
+      <c r="K18">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A19">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A20">
+        <v>19</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
+  <drawing r:id="rId2"/>
+  <tableParts count="1">
+    <tablePart r:id="rId3"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{871083A3-6183-4CF5-AD3C-3324FBE62320}">
+  <dimension ref="A1:F20"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <v>482948</v>
+      </c>
+      <c r="C3">
+        <v>360080</v>
+      </c>
+      <c r="D3">
+        <v>495374</v>
+      </c>
+      <c r="E3">
+        <v>404272</v>
+      </c>
+      <c r="F3">
+        <v>347530</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4">
+        <v>555447</v>
+      </c>
+      <c r="C4">
+        <v>382754</v>
+      </c>
+      <c r="D4">
+        <v>540444</v>
+      </c>
+      <c r="E4">
+        <v>482904</v>
+      </c>
+      <c r="F4">
+        <v>381748</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5">
+        <v>422011</v>
+      </c>
+      <c r="C5">
+        <v>317924</v>
+      </c>
+      <c r="D5">
+        <v>505057</v>
+      </c>
+      <c r="E5">
+        <v>430776</v>
+      </c>
+      <c r="F5">
+        <v>309522</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A6">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A7">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A8">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A9">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A10">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A11">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A12">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A13">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A14">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A15">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A16">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A17">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A18">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A19">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A20">
+        <v>19</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
+</worksheet>
 </file>